--- a/data/data_yearly.xlsx
+++ b/data/data_yearly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\economics\GIT\monmacro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572899CC-4B9C-46FB-B377-059A0E64325D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C749AE65-A233-428C-A715-A05A7959CC3F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6F2A1F3C-C759-48B2-83D1-203BF7CAF231}"/>
   </bookViews>
@@ -1270,7 +1270,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="1">
-        <v>23.584883699999999</v>
+        <v>23.8</v>
       </c>
       <c r="C46">
         <v>23.669</v>
@@ -1279,6 +1279,9 @@
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>50</v>
+      </c>
+      <c r="B47" s="1">
+        <v>25.37</v>
       </c>
       <c r="C47">
         <v>27.242000000000001</v>

--- a/data/data_yearly.xlsx
+++ b/data/data_yearly.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\economics\GIT\monmacro\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\economics\GIT\mon_macro_dash\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C749AE65-A233-428C-A715-A05A7959CC3F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12916DA1-F09F-4035-8E3B-51327080FD35}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6F2A1F3C-C759-48B2-83D1-203BF7CAF231}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>80Y01</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>29Y01</t>
+  </si>
+  <si>
+    <t>gdp_nom_pc</t>
+  </si>
+  <si>
+    <t>gdp_nom_pc_usd</t>
   </si>
 </sst>
 </file>
@@ -554,13 +560,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA43CD4-636F-4C75-AC0B-38C63B2225E1}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>45</v>
       </c>
@@ -576,8 +583,14 @@
       <c r="F1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -585,7 +598,7 @@
         <v>2.7280000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -593,7 +606,7 @@
         <v>2.8540000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -601,7 +614,7 @@
         <v>2.9630000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -609,7 +622,7 @@
         <v>3.0710000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -617,7 +630,7 @@
         <v>2.8370000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -625,7 +638,7 @@
         <v>3.294</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -633,7 +646,7 @@
         <v>3.6360000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -641,7 +654,7 @@
         <v>4.0860000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -649,7 +662,7 @@
         <v>4.1040000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -657,7 +670,7 @@
         <v>4.2750000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -667,8 +680,14 @@
       <c r="C12">
         <v>2.6779999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="1">
+        <v>6.0180110000000002E-3</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.288653</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -678,8 +697,14 @@
       <c r="C13">
         <v>2.8210000000000002</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="1">
+        <v>1.0614272000000001E-2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.3248520000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,8 +714,14 @@
       <c r="C14">
         <v>1.5660000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="1">
+        <v>2.5879355E-2</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.72221500000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -700,8 +731,14 @@
       <c r="C15">
         <v>0.77100000000000002</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="1">
+        <v>0.104005211</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.35230399999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -711,8 +748,14 @@
       <c r="C16">
         <v>0.92600000000000005</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="1">
+        <v>0.17291510800000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.41919799999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -731,8 +774,14 @@
       <c r="F17">
         <v>33.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="1">
+        <v>0.29043974300000003</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.64744100000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -751,8 +800,14 @@
       <c r="F18">
         <v>33.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="1">
+        <v>0.32424931000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.59243899999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -771,8 +826,14 @@
       <c r="F19">
         <v>33.1</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1">
+        <v>0.40430453199999999</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.51195400000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -791,8 +852,14 @@
       <c r="F20">
         <v>32.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="1">
+        <v>0.40402011700000001</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.48091699999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -811,8 +878,14 @@
       <c r="F21">
         <v>32.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="1">
+        <v>0.45524972399999997</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.445544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -831,8 +904,14 @@
       <c r="F22">
         <v>32.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="1">
+        <v>0.50936688200000002</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.47319799999999995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -851,8 +930,14 @@
       <c r="F23">
         <v>32.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="1">
+        <v>0.57222488800000004</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.52131700000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -871,8 +956,14 @@
       <c r="F24">
         <v>32.6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="1">
+        <v>0.62888305200000005</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.56640299999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -891,8 +982,14 @@
       <c r="F25">
         <v>43.4</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="1">
+        <v>0.73306833299999996</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.63937300000000008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -911,8 +1008,14 @@
       <c r="F26">
         <v>43.4</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="1">
+        <v>0.93632315599999993</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.78995799999999994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -931,8 +1034,14 @@
       <c r="F27">
         <v>43.4</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="1">
+        <v>1.1922027560000001</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.98917699999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -951,8 +1060,14 @@
       <c r="F28">
         <v>43.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="1">
+        <v>1.5591027830000002</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1.3216060000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -971,8 +1086,14 @@
       <c r="F29">
         <v>43.4</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="1">
+        <v>1.8915280449999998</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1.6161379999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -991,8 +1112,14 @@
       <c r="F30">
         <v>46.6</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="1">
+        <v>2.4589947689999998</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2.1092689999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1011,8 +1138,14 @@
       <c r="F31">
         <v>49.6</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="1">
+        <v>2.4263512349999998</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1.6875499999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1031,8 +1164,14 @@
       <c r="F32">
         <v>49</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="1">
+        <v>3.533756458</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2.602373</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -1051,8 +1190,14 @@
       <c r="F33">
         <v>43.2</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="1">
+        <v>4.6853941040000002</v>
+      </c>
+      <c r="H33" s="1">
+        <v>3.702359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1071,8 +1216,14 @@
       <c r="F34">
         <v>35.4</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="1">
+        <v>5.819354691</v>
+      </c>
+      <c r="H34" s="1">
+        <v>4.2813299999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -1091,8 +1242,14 @@
       <c r="F35">
         <v>35.4</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="1">
+        <v>6.5434914510000004</v>
+      </c>
+      <c r="H35" s="1">
+        <v>4.2938339999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -1111,8 +1268,14 @@
       <c r="F36">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="1">
+        <v>7.4190362719999996</v>
+      </c>
+      <c r="H36" s="1">
+        <v>4.0810149999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1131,8 +1294,14 @@
       <c r="F37">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="1">
+        <v>7.487391498</v>
+      </c>
+      <c r="H37" s="1">
+        <v>3.8001100000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -1151,8 +1320,14 @@
       <c r="F38">
         <v>34.9</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="1">
+        <v>7.6704619170000008</v>
+      </c>
+      <c r="H38" s="1">
+        <v>3.5750949999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1171,8 +1346,14 @@
       <c r="F39">
         <v>34.9</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="1">
+        <v>8.8142230129999994</v>
+      </c>
+      <c r="H39" s="1">
+        <v>3.6127159999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1191,8 +1372,14 @@
       <c r="F40">
         <v>30.8</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="1">
+        <v>10.061090129</v>
+      </c>
+      <c r="H40" s="1">
+        <v>4.078182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1211,8 +1398,14 @@
       <c r="F41">
         <v>30.8</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="1">
+        <v>11.477331927</v>
+      </c>
+      <c r="H41" s="1">
+        <v>4.3090489999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1231,8 +1424,14 @@
       <c r="F42">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="1">
+        <v>11.154968544999999</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3.9650970000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1242,8 +1441,14 @@
       <c r="C43">
         <v>15.286</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="1">
+        <v>12.773097846999999</v>
+      </c>
+      <c r="H43" s="1">
+        <v>4.4828530000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -1253,8 +1458,14 @@
       <c r="C44">
         <v>17.146000000000001</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="1">
+        <v>15.575067765</v>
+      </c>
+      <c r="H44" s="1">
+        <v>4.9591409999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -1264,8 +1475,14 @@
       <c r="C45">
         <v>20.315000000000001</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="1">
+        <v>20.098921975000003</v>
+      </c>
+      <c r="H45" s="1">
+        <v>5.7964759999999993</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1275,8 +1492,14 @@
       <c r="C46">
         <v>23.669</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="1">
+        <v>22.755093254999998</v>
+      </c>
+      <c r="H46" s="1">
+        <v>6.7124550000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1286,41 +1509,63 @@
       <c r="C47">
         <v>27.242000000000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="1">
+        <v>25.096758803</v>
+      </c>
+      <c r="H47" s="1">
+        <v>7.0793190000000008</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="C48">
         <v>29.12</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="C49">
         <v>31.568999999999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="C50">
         <v>34.024000000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="C51">
         <v>36.4</v>
       </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>